--- a/Futures.xlsx
+++ b/Futures.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parva\Desktop\PDFs\DRM\DRM_Project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56198DB9-DC66-4CC0-A593-3B5F0E611813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Febuary Futures" sheetId="1" r:id="rId1"/>
     <sheet name="March Futures" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -38,11 +32,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,21 +74,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -132,7 +118,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -166,7 +152,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -201,10 +186,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -377,14 +361,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -398,12 +379,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>46023</v>
       </c>
       <c r="B2">
-        <v>44.594549999999998</v>
+        <v>44.59455</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -412,12 +393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>46024</v>
       </c>
       <c r="B3">
-        <v>46.042425000000001</v>
+        <v>46.042425</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -426,12 +407,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>46027</v>
       </c>
       <c r="B4">
-        <v>42.329925000000003</v>
+        <v>42.329925</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -440,12 +421,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>46028</v>
       </c>
       <c r="B5">
-        <v>40.332599999999992</v>
+        <v>40.33259999999999</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -454,12 +435,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>46029</v>
       </c>
       <c r="B6">
-        <v>38.209049999999998</v>
+        <v>38.20905</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -468,12 +449,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>46030</v>
       </c>
       <c r="B7">
-        <v>37.919474999999998</v>
+        <v>37.919475</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -482,12 +463,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>46031</v>
       </c>
       <c r="B8">
-        <v>36.738900000000008</v>
+        <v>36.73890000000001</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -496,12 +477,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>46034</v>
       </c>
       <c r="B9">
-        <v>36.434474999999992</v>
+        <v>36.43447499999999</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -510,12 +491,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>46035</v>
       </c>
       <c r="B10">
-        <v>36.278550000000003</v>
+        <v>36.27855</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -524,12 +505,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>46036</v>
       </c>
       <c r="B11">
-        <v>34.652475000000003</v>
+        <v>34.652475</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -538,12 +519,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>46038</v>
       </c>
       <c r="B12">
-        <v>35.469224999999987</v>
+        <v>35.46922499999999</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -552,12 +533,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>46041</v>
       </c>
       <c r="B13">
-        <v>34.578225000000003</v>
+        <v>34.578225</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -566,12 +547,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>46042</v>
       </c>
       <c r="B14">
-        <v>35.046000000000006</v>
+        <v>35.04600000000001</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -580,12 +561,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>46043</v>
       </c>
       <c r="B15">
-        <v>33.664949999999997</v>
+        <v>33.66495</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -594,12 +575,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>46044</v>
       </c>
       <c r="B16">
-        <v>33.509025000000001</v>
+        <v>33.509025</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -608,12 +589,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>46045</v>
       </c>
       <c r="B17">
-        <v>32.811075000000002</v>
+        <v>32.811075</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -622,12 +603,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>46049</v>
       </c>
       <c r="B18">
-        <v>34.466849999999987</v>
+        <v>34.46684999999999</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -636,12 +617,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>46050</v>
       </c>
       <c r="B19">
-        <v>34.971750000000007</v>
+        <v>34.97175000000001</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -650,12 +631,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>46051</v>
       </c>
       <c r="B20">
-        <v>35.640000000000008</v>
+        <v>35.64000000000001</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -664,12 +645,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>46052</v>
       </c>
       <c r="B21">
-        <v>34.622774999999997</v>
+        <v>34.622775</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -684,14 +665,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -705,12 +683,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>46023</v>
       </c>
       <c r="B2">
-        <v>44.879669999999997</v>
+        <v>44.87967</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -719,12 +697,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>46024</v>
       </c>
       <c r="B3">
-        <v>46.312694999999998</v>
+        <v>46.312695</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -733,12 +711,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>46027</v>
       </c>
       <c r="B4">
-        <v>42.600194999999999</v>
+        <v>42.600195</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -747,12 +725,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>46028</v>
       </c>
       <c r="B5">
-        <v>40.647419999999997</v>
+        <v>40.64742</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -761,12 +739,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>46029</v>
       </c>
       <c r="B6">
-        <v>38.405070000000002</v>
+        <v>38.40507</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -775,12 +753,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>46030</v>
       </c>
       <c r="B7">
-        <v>38.204595000000012</v>
+        <v>38.20459500000001</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -789,12 +767,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>46031</v>
       </c>
       <c r="B8">
-        <v>37.024020000000007</v>
+        <v>37.02402000000001</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -803,12 +781,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>46034</v>
       </c>
       <c r="B9">
-        <v>36.853245000000022</v>
+        <v>36.85324500000002</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -817,12 +795,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>46035</v>
       </c>
       <c r="B10">
-        <v>36.496845000000022</v>
+        <v>36.49684500000002</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -831,12 +809,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>46036</v>
       </c>
       <c r="B11">
-        <v>34.855920000000012</v>
+        <v>34.85592000000001</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -845,12 +823,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>46038</v>
       </c>
       <c r="B12">
-        <v>35.672670000000011</v>
+        <v>35.67267000000001</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -859,12 +837,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>46041</v>
       </c>
       <c r="B13">
-        <v>34.818795000000009</v>
+        <v>34.81879500000001</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -873,12 +851,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>46042</v>
       </c>
       <c r="B14">
-        <v>35.242020000000011</v>
+        <v>35.24202000000001</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -887,12 +865,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>46043</v>
       </c>
       <c r="B15">
-        <v>33.883245000000016</v>
+        <v>33.88324500000002</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -901,12 +879,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>46044</v>
       </c>
       <c r="B16">
-        <v>33.808995000000017</v>
+        <v>33.80899500000002</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -915,12 +893,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>46045</v>
       </c>
       <c r="B17">
-        <v>33.029370000000021</v>
+        <v>33.02937000000002</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -929,12 +907,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>46049</v>
       </c>
       <c r="B18">
-        <v>34.662870000000019</v>
+        <v>34.66287000000002</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -943,12 +921,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>46050</v>
       </c>
       <c r="B19">
-        <v>35.204895000000008</v>
+        <v>35.20489500000001</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -957,12 +935,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>46051</v>
       </c>
       <c r="B20">
-        <v>35.858295000000012</v>
+        <v>35.85829500000001</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -971,12 +949,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>46052</v>
       </c>
       <c r="B21">
-        <v>34.855920000000012</v>
+        <v>34.85592000000001</v>
       </c>
       <c r="C21">
         <v>0</v>
